--- a/upload/licitacoes2026.xlsx
+++ b/upload/licitacoes2026.xlsx
@@ -154,6 +154,7 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
